--- a/ROSA_vitaSPEC/Results/test_pretraitements/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_diff.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Pretraitement</t>
   </si>
@@ -133,18 +133,6 @@
   </si>
   <si>
     <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
   </si>
   <si>
     <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
@@ -211,7 +199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,13 +211,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -255,37 +236,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -616,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
@@ -678,49 +638,49 @@
         <v>16</v>
       </c>
       <c r="B2">
-        <v>3.6937771832595001E-2</v>
+        <v>3.7113717745297703E-2</v>
       </c>
       <c r="C2">
-        <v>6.1182649317331139E-2</v>
+        <v>5.7799545459113089E-2</v>
       </c>
       <c r="D2">
-        <v>8.4073144716608372E-2</v>
+        <v>8.1317052878041973E-2</v>
       </c>
       <c r="E2">
-        <v>8.5032791176046008E-2</v>
+        <v>8.3466621273078911E-2</v>
       </c>
       <c r="F2">
-        <v>0.1158098921255746</v>
+        <v>0.110633689642212</v>
       </c>
       <c r="G2">
-        <v>0.12537106728725839</v>
+        <v>0.11736271883718</v>
       </c>
       <c r="H2">
-        <v>0.13843730393211781</v>
+        <v>0.13070443905420229</v>
       </c>
       <c r="I2">
-        <v>0.14883918461743181</v>
+        <v>0.14125272071878031</v>
       </c>
       <c r="J2">
-        <v>0.1485373535240179</v>
+        <v>0.1401096121794814</v>
       </c>
       <c r="K2">
-        <v>0.1665778757076648</v>
+        <v>0.15777807345330311</v>
       </c>
       <c r="L2">
-        <v>0.19519187359633219</v>
+        <v>0.18588568060319829</v>
       </c>
       <c r="M2">
-        <v>0.24357347559636841</v>
+        <v>0.23491993120911711</v>
       </c>
       <c r="N2">
-        <v>0.33588743634742613</v>
+        <v>0.327897250386251</v>
       </c>
       <c r="O2">
-        <v>0.44336055388554091</v>
+        <v>0.43916057459414282</v>
       </c>
       <c r="P2">
-        <v>0.47794039671820848</v>
+        <v>0.47381638396022008</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -728,49 +688,49 @@
         <v>17</v>
       </c>
       <c r="B3">
-        <v>4.4627700237565127E-2</v>
+        <v>4.2677620296663943E-2</v>
       </c>
       <c r="C3">
-        <v>4.2625857214722951E-2</v>
+        <v>4.3143789168492652E-2</v>
       </c>
       <c r="D3">
-        <v>7.7624076090464511E-2</v>
+        <v>8.0140550623583606E-2</v>
       </c>
       <c r="E3">
-        <v>0.1801463631745662</v>
+        <v>0.17626897162658969</v>
       </c>
       <c r="F3">
-        <v>0.1967137381110553</v>
+        <v>0.1931320323008599</v>
       </c>
       <c r="G3">
-        <v>0.22816247449197011</v>
+        <v>0.22248022843251611</v>
       </c>
       <c r="H3">
-        <v>0.26095890973873392</v>
+        <v>0.25691783763173559</v>
       </c>
       <c r="I3">
-        <v>0.29346088949163002</v>
+        <v>0.29295237791588158</v>
       </c>
       <c r="J3">
-        <v>0.33851493888248158</v>
+        <v>0.34057626320005591</v>
       </c>
       <c r="K3">
-        <v>0.39958165484535491</v>
+        <v>0.40286115506590497</v>
       </c>
       <c r="L3">
-        <v>0.4655988639665497</v>
+        <v>0.47139420195726423</v>
       </c>
       <c r="M3">
-        <v>0.52472515688336085</v>
+        <v>0.53106024321133072</v>
       </c>
       <c r="N3">
-        <v>0.58235566489502433</v>
+        <v>0.58593364889621236</v>
       </c>
       <c r="O3">
-        <v>0.6043248517222306</v>
+        <v>0.61426474050444591</v>
       </c>
       <c r="P3">
-        <v>0.60306086662856973</v>
+        <v>0.61319103169019473</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -778,49 +738,49 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>3.5737730064117117E-2</v>
+        <v>3.7156490888305527E-2</v>
       </c>
       <c r="C4">
-        <v>5.5531660802940967E-2</v>
+        <v>5.6702933994972733E-2</v>
       </c>
       <c r="D4">
-        <v>7.0328121477996552E-2</v>
+        <v>6.9232894585019578E-2</v>
       </c>
       <c r="E4">
-        <v>0.13155117867033009</v>
+        <v>0.1271705113946287</v>
       </c>
       <c r="F4">
-        <v>0.1394679582051343</v>
+        <v>0.13493063628684829</v>
       </c>
       <c r="G4">
-        <v>0.1170094796921356</v>
+        <v>0.11628269054015029</v>
       </c>
       <c r="H4">
-        <v>0.12531521326949061</v>
+        <v>0.12633485287868729</v>
       </c>
       <c r="I4">
-        <v>0.13998411084830051</v>
+        <v>0.1406129797166322</v>
       </c>
       <c r="J4">
-        <v>0.20060072487956099</v>
+        <v>0.20563662151889839</v>
       </c>
       <c r="K4">
-        <v>0.25736101182575388</v>
+        <v>0.26517624388955219</v>
       </c>
       <c r="L4">
-        <v>0.29026310697744651</v>
+        <v>0.30089129969874839</v>
       </c>
       <c r="M4">
-        <v>0.37660822764269319</v>
+        <v>0.39380631100257552</v>
       </c>
       <c r="N4">
-        <v>0.45879465748813891</v>
+        <v>0.47590589462261751</v>
       </c>
       <c r="O4">
-        <v>0.52084608386729347</v>
+        <v>0.53526814304770132</v>
       </c>
       <c r="P4">
-        <v>0.57512390229277588</v>
+        <v>0.58552862890217772</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -828,49 +788,49 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>2.893566008314025E-2</v>
+        <v>3.1631847143537888E-2</v>
       </c>
       <c r="C5">
-        <v>7.7831989996713091E-2</v>
+        <v>8.2222511121640862E-2</v>
       </c>
       <c r="D5">
-        <v>0.1197044435104371</v>
+        <v>0.12451360432753911</v>
       </c>
       <c r="E5">
-        <v>0.14427166596743171</v>
+        <v>0.15209256877757241</v>
       </c>
       <c r="F5">
-        <v>0.17045402291793599</v>
+        <v>0.17293620462588319</v>
       </c>
       <c r="G5">
-        <v>0.17754940158418259</v>
+        <v>0.1811212020188436</v>
       </c>
       <c r="H5">
-        <v>0.1908066059334288</v>
+        <v>0.1940708212703455</v>
       </c>
       <c r="I5">
-        <v>0.21965267603513841</v>
+        <v>0.22395447185443901</v>
       </c>
       <c r="J5">
-        <v>0.28480771101209701</v>
+        <v>0.29526133762123452</v>
       </c>
       <c r="K5">
-        <v>0.34742601116416683</v>
+        <v>0.36216963931465468</v>
       </c>
       <c r="L5">
-        <v>0.39208026386076811</v>
+        <v>0.41136418610579728</v>
       </c>
       <c r="M5">
-        <v>0.41955024477298569</v>
+        <v>0.44121628397653467</v>
       </c>
       <c r="N5">
-        <v>0.42533523559865072</v>
+        <v>0.44889621294315452</v>
       </c>
       <c r="O5">
-        <v>0.45143475452174958</v>
+        <v>0.47555366661825088</v>
       </c>
       <c r="P5">
-        <v>0.48153682914592177</v>
+        <v>0.50283569867928091</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -878,49 +838,49 @@
         <v>20</v>
       </c>
       <c r="B6">
-        <v>3.0603212452403439E-2</v>
+        <v>2.890541683351194E-2</v>
       </c>
       <c r="C6">
-        <v>7.5258697410288955E-2</v>
+        <v>7.2192129079884537E-2</v>
       </c>
       <c r="D6">
-        <v>0.1127474064428419</v>
+        <v>0.10990318846442609</v>
       </c>
       <c r="E6">
-        <v>0.12814758128624201</v>
+        <v>0.13059081298949979</v>
       </c>
       <c r="F6">
-        <v>0.13448339203267581</v>
+        <v>0.1324662737192247</v>
       </c>
       <c r="G6">
-        <v>0.16664879051106141</v>
+        <v>0.16676727237234359</v>
       </c>
       <c r="H6">
-        <v>0.17300604848801479</v>
+        <v>0.1700371832540872</v>
       </c>
       <c r="I6">
-        <v>0.21801518296718689</v>
+        <v>0.21776772497439051</v>
       </c>
       <c r="J6">
-        <v>0.2857014587019745</v>
+        <v>0.28441119336644782</v>
       </c>
       <c r="K6">
-        <v>0.31124827812910572</v>
+        <v>0.30781540817475678</v>
       </c>
       <c r="L6">
-        <v>0.36011621570635549</v>
+        <v>0.35917652373157127</v>
       </c>
       <c r="M6">
-        <v>0.3924376168374113</v>
+        <v>0.39537293632819859</v>
       </c>
       <c r="N6">
-        <v>0.44043524608582052</v>
+        <v>0.43964342700363951</v>
       </c>
       <c r="O6">
-        <v>0.46867180408604292</v>
+        <v>0.46359941987243558</v>
       </c>
       <c r="P6">
-        <v>0.5104683295998993</v>
+        <v>0.50707066094043296</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -928,49 +888,49 @@
         <v>21</v>
       </c>
       <c r="B7">
-        <v>3.8274028969187128E-2</v>
+        <v>3.6432264636905132E-2</v>
       </c>
       <c r="C7">
-        <v>5.602201598453399E-2</v>
+        <v>5.4084389521506897E-2</v>
       </c>
       <c r="D7">
-        <v>8.5330923585568708E-2</v>
+        <v>8.3537477191074516E-2</v>
       </c>
       <c r="E7">
-        <v>8.1403910513440425E-2</v>
+        <v>7.8641151368945228E-2</v>
       </c>
       <c r="F7">
-        <v>9.8896298633896151E-2</v>
+        <v>9.7430273023103475E-2</v>
       </c>
       <c r="G7">
-        <v>9.6726577471556219E-2</v>
+        <v>9.5875421759333612E-2</v>
       </c>
       <c r="H7">
-        <v>0.1202988532508595</v>
+        <v>0.1191306823644053</v>
       </c>
       <c r="I7">
-        <v>0.12531238740735401</v>
+        <v>0.1242964930380497</v>
       </c>
       <c r="J7">
-        <v>0.14247068829851131</v>
+        <v>0.14211152145019909</v>
       </c>
       <c r="K7">
-        <v>0.19822028291382709</v>
+        <v>0.19844609897775911</v>
       </c>
       <c r="L7">
-        <v>0.2417453456488213</v>
+        <v>0.24213745838026629</v>
       </c>
       <c r="M7">
-        <v>0.27076128479258349</v>
+        <v>0.26978492521630282</v>
       </c>
       <c r="N7">
-        <v>0.35944844662058362</v>
+        <v>0.35828029120161842</v>
       </c>
       <c r="O7">
-        <v>0.44755858477881399</v>
+        <v>0.44604644810356081</v>
       </c>
       <c r="P7">
-        <v>0.5103983783320577</v>
+        <v>0.50584199862954393</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -978,49 +938,49 @@
         <v>22</v>
       </c>
       <c r="B8">
-        <v>3.313872306243798E-2</v>
+        <v>3.309564975098378E-2</v>
       </c>
       <c r="C8">
-        <v>5.1220131762069188E-2</v>
+        <v>5.1618044582608602E-2</v>
       </c>
       <c r="D8">
-        <v>8.270293271873419E-2</v>
+        <v>8.4415064065691769E-2</v>
       </c>
       <c r="E8">
-        <v>9.2117891676026464E-2</v>
+        <v>9.5654176148654013E-2</v>
       </c>
       <c r="F8">
-        <v>9.9950569470477979E-2</v>
+        <v>0.1045968234136658</v>
       </c>
       <c r="G8">
-        <v>0.1324545910856931</v>
+        <v>0.13840545510510699</v>
       </c>
       <c r="H8">
-        <v>0.13603111541840909</v>
+        <v>0.14440131665355471</v>
       </c>
       <c r="I8">
-        <v>0.1619192142991516</v>
+        <v>0.17087312097165841</v>
       </c>
       <c r="J8">
-        <v>0.2190495149987787</v>
+        <v>0.2297822698854978</v>
       </c>
       <c r="K8">
-        <v>0.30251235990127828</v>
+        <v>0.31379431050006601</v>
       </c>
       <c r="L8">
-        <v>0.34302339620591737</v>
+        <v>0.3589370078723701</v>
       </c>
       <c r="M8">
-        <v>0.38913812749615873</v>
+        <v>0.40204839949758148</v>
       </c>
       <c r="N8">
-        <v>0.47385784678570758</v>
+        <v>0.48403174205232452</v>
       </c>
       <c r="O8">
-        <v>0.54831516501588551</v>
+        <v>0.55048233333661978</v>
       </c>
       <c r="P8">
-        <v>0.62866421262630112</v>
+        <v>0.62988529435063878</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1028,49 +988,49 @@
         <v>23</v>
       </c>
       <c r="B9">
-        <v>3.0531207445679609E-2</v>
+        <v>3.3033451525491753E-2</v>
       </c>
       <c r="C9">
-        <v>4.9010383166133487E-2</v>
+        <v>4.9090799437173933E-2</v>
       </c>
       <c r="D9">
-        <v>8.4281137112591109E-2</v>
+        <v>8.0861881684199388E-2</v>
       </c>
       <c r="E9">
-        <v>9.3766604336287251E-2</v>
+        <v>9.100890390341021E-2</v>
       </c>
       <c r="F9">
-        <v>0.1023705916875933</v>
+        <v>9.9900002435763025E-2</v>
       </c>
       <c r="G9">
-        <v>0.1311945769592717</v>
+        <v>0.12878867859244381</v>
       </c>
       <c r="H9">
-        <v>0.12703733012679061</v>
+        <v>0.12732843796998539</v>
       </c>
       <c r="I9">
-        <v>0.14297724897100461</v>
+        <v>0.14209780694887231</v>
       </c>
       <c r="J9">
-        <v>0.1588174503707791</v>
+        <v>0.1588566938233785</v>
       </c>
       <c r="K9">
-        <v>0.20153351012952159</v>
+        <v>0.19845267735415101</v>
       </c>
       <c r="L9">
-        <v>0.2383234283842823</v>
+        <v>0.2347790415154748</v>
       </c>
       <c r="M9">
-        <v>0.28135043621216771</v>
+        <v>0.27210820042876038</v>
       </c>
       <c r="N9">
-        <v>0.3345963226528475</v>
+        <v>0.32718220249743352</v>
       </c>
       <c r="O9">
-        <v>0.35564761768369219</v>
+        <v>0.35289270000501188</v>
       </c>
       <c r="P9">
-        <v>0.37962855204013651</v>
+        <v>0.3773703506907885</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1078,49 +1038,49 @@
         <v>24</v>
       </c>
       <c r="B10">
-        <v>3.1993379844500791E-2</v>
+        <v>3.045777259126237E-2</v>
       </c>
       <c r="C10">
-        <v>5.0227350340144188E-2</v>
+        <v>4.8104484073793967E-2</v>
       </c>
       <c r="D10">
-        <v>8.3641460909848364E-2</v>
+        <v>8.4067969286155342E-2</v>
       </c>
       <c r="E10">
-        <v>9.2016460750982243E-2</v>
+        <v>9.4585847552270397E-2</v>
       </c>
       <c r="F10">
-        <v>9.901307783419222E-2</v>
+        <v>0.1032035480965785</v>
       </c>
       <c r="G10">
-        <v>0.12992064400444531</v>
+        <v>0.1311574736051172</v>
       </c>
       <c r="H10">
-        <v>0.1242239882344017</v>
+        <v>0.12651206723614691</v>
       </c>
       <c r="I10">
-        <v>0.14329685034865181</v>
+        <v>0.14278347383856879</v>
       </c>
       <c r="J10">
-        <v>0.15752985341996939</v>
+        <v>0.15877284842597669</v>
       </c>
       <c r="K10">
-        <v>0.19373982826906361</v>
+        <v>0.19609535869809841</v>
       </c>
       <c r="L10">
-        <v>0.22710623508503719</v>
+        <v>0.23046199984494259</v>
       </c>
       <c r="M10">
-        <v>0.25536769230424111</v>
+        <v>0.26615677310180341</v>
       </c>
       <c r="N10">
-        <v>0.30015229696283702</v>
+        <v>0.31094750227401191</v>
       </c>
       <c r="O10">
-        <v>0.32355479342471449</v>
+        <v>0.33477386663099062</v>
       </c>
       <c r="P10">
-        <v>0.35299392929894952</v>
+        <v>0.36643183281510272</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1128,49 +1088,49 @@
         <v>25</v>
       </c>
       <c r="B11">
-        <v>2.9778829414645661E-2</v>
+        <v>3.450866779059969E-2</v>
       </c>
       <c r="C11">
-        <v>4.6448067677397453E-2</v>
+        <v>5.0619192354169007E-2</v>
       </c>
       <c r="D11">
-        <v>7.9334118841400847E-2</v>
+        <v>8.6005419891240442E-2</v>
       </c>
       <c r="E11">
-        <v>9.0216268814516831E-2</v>
+        <v>9.6300073751265258E-2</v>
       </c>
       <c r="F11">
-        <v>9.8211911015106401E-2</v>
+        <v>0.10388526291922941</v>
       </c>
       <c r="G11">
-        <v>0.12537245985768869</v>
+        <v>0.13148420552310561</v>
       </c>
       <c r="H11">
-        <v>0.12472225564713491</v>
+        <v>0.13107083976188369</v>
       </c>
       <c r="I11">
-        <v>0.13970822805757521</v>
+        <v>0.14519509693206889</v>
       </c>
       <c r="J11">
-        <v>0.15758868928323219</v>
+        <v>0.1628153542101376</v>
       </c>
       <c r="K11">
-        <v>0.20089959432354401</v>
+        <v>0.20611142147165101</v>
       </c>
       <c r="L11">
-        <v>0.23392534484748889</v>
+        <v>0.23662774893713079</v>
       </c>
       <c r="M11">
-        <v>0.26711056205538081</v>
+        <v>0.26950162850449672</v>
       </c>
       <c r="N11">
-        <v>0.30848968000321653</v>
+        <v>0.30880171866990819</v>
       </c>
       <c r="O11">
-        <v>0.3238501266529667</v>
+        <v>0.32230465327490232</v>
       </c>
       <c r="P11">
-        <v>0.35751717019229468</v>
+        <v>0.35591783692216478</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1178,49 +1138,49 @@
         <v>26</v>
       </c>
       <c r="B12">
-        <v>3.1594113210958293E-2</v>
+        <v>2.78996939965655E-2</v>
       </c>
       <c r="C12">
-        <v>9.8399324236440655E-2</v>
+        <v>9.8286754210170191E-2</v>
       </c>
       <c r="D12">
-        <v>0.11620514711367599</v>
+        <v>0.11521903167894131</v>
       </c>
       <c r="E12">
-        <v>0.13239597414685109</v>
+        <v>0.1335653016349049</v>
       </c>
       <c r="F12">
-        <v>0.15212744603410289</v>
+        <v>0.14628889845184381</v>
       </c>
       <c r="G12">
-        <v>0.16007531479231829</v>
+        <v>0.15487516555537051</v>
       </c>
       <c r="H12">
-        <v>0.16932637317160101</v>
+        <v>0.16457395976926331</v>
       </c>
       <c r="I12">
-        <v>0.20331137325205481</v>
+        <v>0.19855518382347279</v>
       </c>
       <c r="J12">
-        <v>0.25091133726517778</v>
+        <v>0.24555067456252719</v>
       </c>
       <c r="K12">
-        <v>0.33253636672184411</v>
+        <v>0.32813796368981257</v>
       </c>
       <c r="L12">
-        <v>0.39522108045244259</v>
+        <v>0.38580230461605608</v>
       </c>
       <c r="M12">
-        <v>0.448106799506442</v>
+        <v>0.44054412123995051</v>
       </c>
       <c r="N12">
-        <v>0.46097987173207278</v>
+        <v>0.45601083104527768</v>
       </c>
       <c r="O12">
-        <v>0.51138388856275219</v>
+        <v>0.50141992308030892</v>
       </c>
       <c r="P12">
-        <v>0.57953959804937139</v>
+        <v>0.56669186189669019</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1228,49 +1188,49 @@
         <v>27</v>
       </c>
       <c r="B13">
-        <v>3.1800545914208937E-2</v>
+        <v>2.986393664618819E-2</v>
       </c>
       <c r="C13">
-        <v>0.1319616015663137</v>
+        <v>0.13361826304278479</v>
       </c>
       <c r="D13">
-        <v>0.13048251406854011</v>
+        <v>0.1328441276887046</v>
       </c>
       <c r="E13">
-        <v>0.17263045384820899</v>
+        <v>0.17050534333459039</v>
       </c>
       <c r="F13">
-        <v>0.2282571509038509</v>
+        <v>0.23413527314983251</v>
       </c>
       <c r="G13">
-        <v>0.23027679398904549</v>
+        <v>0.2332273204731086</v>
       </c>
       <c r="H13">
-        <v>0.22607914939605239</v>
+        <v>0.23098937168845071</v>
       </c>
       <c r="I13">
-        <v>0.24738933427447971</v>
+        <v>0.25197911995369809</v>
       </c>
       <c r="J13">
-        <v>0.29202286787538412</v>
+        <v>0.29977718403632497</v>
       </c>
       <c r="K13">
-        <v>0.38023808979312568</v>
+        <v>0.38531464318014241</v>
       </c>
       <c r="L13">
-        <v>0.44420964885320419</v>
+        <v>0.44350882063376651</v>
       </c>
       <c r="M13">
-        <v>0.47290114478726819</v>
+        <v>0.47064592156913521</v>
       </c>
       <c r="N13">
-        <v>0.52762906491688444</v>
+        <v>0.52288266537882921</v>
       </c>
       <c r="O13">
-        <v>0.57611452042637534</v>
+        <v>0.57063103123530579</v>
       </c>
       <c r="P13">
-        <v>0.64078854986473033</v>
+        <v>0.63293495597383387</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1278,49 +1238,49 @@
         <v>28</v>
       </c>
       <c r="B14">
-        <v>3.4275574930637209E-2</v>
+        <v>3.5553129382294817E-2</v>
       </c>
       <c r="C14">
-        <v>5.311823825505213E-2</v>
+        <v>5.2745770229467137E-2</v>
       </c>
       <c r="D14">
-        <v>8.3031742568943523E-2</v>
+        <v>7.9951843919830345E-2</v>
       </c>
       <c r="E14">
-        <v>7.840201576584005E-2</v>
+        <v>7.7799038760906214E-2</v>
       </c>
       <c r="F14">
-        <v>9.5490541363056125E-2</v>
+        <v>9.4287419430706509E-2</v>
       </c>
       <c r="G14">
-        <v>8.9830124155156454E-2</v>
+        <v>9.0267492872347366E-2</v>
       </c>
       <c r="H14">
-        <v>0.11203881696055849</v>
+        <v>0.1115803129464619</v>
       </c>
       <c r="I14">
-        <v>0.1131652506536741</v>
+        <v>0.1140951559257187</v>
       </c>
       <c r="J14">
-        <v>0.12542501860599889</v>
+        <v>0.12650386870405911</v>
       </c>
       <c r="K14">
-        <v>0.1537725159869904</v>
+        <v>0.1575711939780898</v>
       </c>
       <c r="L14">
-        <v>0.1735331341262111</v>
+        <v>0.1776114195179096</v>
       </c>
       <c r="M14">
-        <v>0.1866912461983837</v>
+        <v>0.1912584068271079</v>
       </c>
       <c r="N14">
-        <v>0.25018749662043149</v>
+        <v>0.25148302574402781</v>
       </c>
       <c r="O14">
-        <v>0.29600913439486798</v>
+        <v>0.2999102638840131</v>
       </c>
       <c r="P14">
-        <v>0.33550447865875133</v>
+        <v>0.33638725725534879</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1328,49 +1288,49 @@
         <v>29</v>
       </c>
       <c r="B15">
-        <v>3.494916481421928E-2</v>
+        <v>3.5870791273118707E-2</v>
       </c>
       <c r="C15">
-        <v>5.3397640909355497E-2</v>
+        <v>5.3636803047532489E-2</v>
       </c>
       <c r="D15">
-        <v>7.9468557551871433E-2</v>
+        <v>8.1929676897593451E-2</v>
       </c>
       <c r="E15">
-        <v>7.3538134643536535E-2</v>
+        <v>7.9876134848400615E-2</v>
       </c>
       <c r="F15">
-        <v>8.8978633711986999E-2</v>
+        <v>9.5655709372115427E-2</v>
       </c>
       <c r="G15">
-        <v>8.8132589884983292E-2</v>
+        <v>9.4739424157337604E-2</v>
       </c>
       <c r="H15">
-        <v>0.10566782039945211</v>
+        <v>0.1133624778843649</v>
       </c>
       <c r="I15">
-        <v>0.1071140039717856</v>
+        <v>0.1136214885957046</v>
       </c>
       <c r="J15">
-        <v>0.11838863514753629</v>
+        <v>0.1242448311103385</v>
       </c>
       <c r="K15">
-        <v>0.144494821657666</v>
+        <v>0.15163370774873319</v>
       </c>
       <c r="L15">
-        <v>0.16152523270405089</v>
+        <v>0.16933183235344679</v>
       </c>
       <c r="M15">
-        <v>0.17388829259265889</v>
+        <v>0.18340863796008591</v>
       </c>
       <c r="N15">
-        <v>0.24910783143189991</v>
+        <v>0.26409982168869989</v>
       </c>
       <c r="O15">
-        <v>0.291164010443757</v>
+        <v>0.3114803657777459</v>
       </c>
       <c r="P15">
-        <v>0.29040860109693217</v>
+        <v>0.31485588245857837</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1378,49 +1338,49 @@
         <v>30</v>
       </c>
       <c r="B16">
-        <v>3.6575992455891097E-2</v>
+        <v>3.2827066368366131E-2</v>
       </c>
       <c r="C16">
-        <v>5.3818149663018573E-2</v>
+        <v>5.0223052844775851E-2</v>
       </c>
       <c r="D16">
-        <v>8.5201477768865552E-2</v>
+        <v>7.8644178360723904E-2</v>
       </c>
       <c r="E16">
-        <v>8.2781301750274205E-2</v>
+        <v>7.6953967576502302E-2</v>
       </c>
       <c r="F16">
-        <v>9.8837961523790319E-2</v>
+        <v>9.121512520440278E-2</v>
       </c>
       <c r="G16">
-        <v>9.383861951163186E-2</v>
+        <v>8.7506307593042898E-2</v>
       </c>
       <c r="H16">
-        <v>0.1157791305846744</v>
+        <v>0.10586082900459</v>
       </c>
       <c r="I16">
-        <v>0.1162707264772114</v>
+        <v>0.1086590637141361</v>
       </c>
       <c r="J16">
-        <v>0.12686543182749321</v>
+        <v>0.11825900392691011</v>
       </c>
       <c r="K16">
-        <v>0.15032172951776221</v>
+        <v>0.14232105644566281</v>
       </c>
       <c r="L16">
-        <v>0.1667895881987892</v>
+        <v>0.15907697683152461</v>
       </c>
       <c r="M16">
-        <v>0.18114465284192779</v>
+        <v>0.17371581124038249</v>
       </c>
       <c r="N16">
-        <v>0.26872983961439939</v>
+        <v>0.25926901860884671</v>
       </c>
       <c r="O16">
-        <v>0.32324187312235042</v>
+        <v>0.31248652772548002</v>
       </c>
       <c r="P16">
-        <v>0.32225290542618368</v>
+        <v>0.31358889614034652</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1428,49 +1388,49 @@
         <v>31</v>
       </c>
       <c r="B17">
-        <v>3.3678686360311627E-2</v>
+        <v>3.2753652349903288E-2</v>
       </c>
       <c r="C17">
-        <v>5.2874545806300133E-2</v>
+        <v>5.0769981463918153E-2</v>
       </c>
       <c r="D17">
-        <v>7.8219830316663796E-2</v>
+        <v>7.5923699468326111E-2</v>
       </c>
       <c r="E17">
-        <v>7.6396065540977776E-2</v>
+        <v>7.3891165581025819E-2</v>
       </c>
       <c r="F17">
-        <v>9.2410577661721449E-2</v>
+        <v>9.0179045874790975E-2</v>
       </c>
       <c r="G17">
-        <v>9.3161323063195356E-2</v>
+        <v>8.7958342205117224E-2</v>
       </c>
       <c r="H17">
-        <v>0.10936850619180929</v>
+        <v>0.10713611903788491</v>
       </c>
       <c r="I17">
-        <v>0.11263374502709519</v>
+        <v>0.1081902148758469</v>
       </c>
       <c r="J17">
-        <v>0.1226729927580501</v>
+        <v>0.1194599384634636</v>
       </c>
       <c r="K17">
-        <v>0.1478990234744437</v>
+        <v>0.1432406662373609</v>
       </c>
       <c r="L17">
-        <v>0.16654391520263931</v>
+        <v>0.15982102137691359</v>
       </c>
       <c r="M17">
-        <v>0.18375733786972259</v>
+        <v>0.17217229423527991</v>
       </c>
       <c r="N17">
-        <v>0.26617160478184748</v>
+        <v>0.24841056655438939</v>
       </c>
       <c r="O17">
-        <v>0.32070375059627593</v>
+        <v>0.30509851543507321</v>
       </c>
       <c r="P17">
-        <v>0.32885527234711032</v>
+        <v>0.30898333895195251</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1478,49 +1438,49 @@
         <v>32</v>
       </c>
       <c r="B18">
-        <v>2.9409928419941941E-2</v>
+        <v>3.0336569026109931E-2</v>
       </c>
       <c r="C18">
-        <v>0.10481426069178409</v>
+        <v>0.1095099220058259</v>
       </c>
       <c r="D18">
-        <v>0.1184578829055007</v>
+        <v>0.12325877181536909</v>
       </c>
       <c r="E18">
-        <v>0.13777787057728461</v>
+        <v>0.14686803337101459</v>
       </c>
       <c r="F18">
-        <v>0.14514390173610381</v>
+        <v>0.14916946504656539</v>
       </c>
       <c r="G18">
-        <v>0.1811731707591564</v>
+        <v>0.18557531505073749</v>
       </c>
       <c r="H18">
-        <v>0.17358512465488371</v>
+        <v>0.17680798862684879</v>
       </c>
       <c r="I18">
-        <v>0.2008847798256862</v>
+        <v>0.2032833063883718</v>
       </c>
       <c r="J18">
-        <v>0.24830135836097569</v>
+        <v>0.25015273180753972</v>
       </c>
       <c r="K18">
-        <v>0.31918175557718481</v>
+        <v>0.32000845792850191</v>
       </c>
       <c r="L18">
-        <v>0.36813425111214659</v>
+        <v>0.36874854493275</v>
       </c>
       <c r="M18">
-        <v>0.40805187980634777</v>
+        <v>0.4035860239589889</v>
       </c>
       <c r="N18">
-        <v>0.40987351468430883</v>
+        <v>0.40162302862170202</v>
       </c>
       <c r="O18">
-        <v>0.43432284045598157</v>
+        <v>0.42528185571075189</v>
       </c>
       <c r="P18">
-        <v>0.46793863133100672</v>
+        <v>0.45809016385454432</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -1528,49 +1488,49 @@
         <v>33</v>
       </c>
       <c r="B19">
-        <v>2.8001613549765329E-2</v>
+        <v>2.8970737065485311E-2</v>
       </c>
       <c r="C19">
-        <v>9.5610945236236144E-2</v>
+        <v>0.10294892171350881</v>
       </c>
       <c r="D19">
-        <v>0.1075420644140815</v>
+        <v>0.11032487640194499</v>
       </c>
       <c r="E19">
-        <v>0.12052032681613679</v>
+        <v>0.1248293351624615</v>
       </c>
       <c r="F19">
-        <v>0.1115577871668845</v>
+        <v>0.1136722246791841</v>
       </c>
       <c r="G19">
-        <v>0.14767099183395119</v>
+        <v>0.15100708608540789</v>
       </c>
       <c r="H19">
-        <v>0.14561848592116111</v>
+        <v>0.14988509318650489</v>
       </c>
       <c r="I19">
-        <v>0.18441047968758001</v>
+        <v>0.18641410348288201</v>
       </c>
       <c r="J19">
-        <v>0.2406657360984458</v>
+        <v>0.23916544366946299</v>
       </c>
       <c r="K19">
-        <v>0.27012465202636571</v>
+        <v>0.2660439629198339</v>
       </c>
       <c r="L19">
-        <v>0.32699842550467012</v>
+        <v>0.32535531509642818</v>
       </c>
       <c r="M19">
-        <v>0.35191026432823369</v>
+        <v>0.35044475413184378</v>
       </c>
       <c r="N19">
-        <v>0.38511958092481102</v>
+        <v>0.38722022599245792</v>
       </c>
       <c r="O19">
-        <v>0.41407669051161111</v>
+        <v>0.41604258409031353</v>
       </c>
       <c r="P19">
-        <v>0.47329821815103501</v>
+        <v>0.47201392060318859</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -1578,49 +1538,49 @@
         <v>34</v>
       </c>
       <c r="B20">
-        <v>2.8712753131029719E-2</v>
+        <v>2.8413785465361659E-2</v>
       </c>
       <c r="C20">
-        <v>9.5138707960219338E-2</v>
+        <v>8.6998353823042274E-2</v>
       </c>
       <c r="D20">
-        <v>0.1006644791415908</v>
+        <v>9.8875577210100984E-2</v>
       </c>
       <c r="E20">
-        <v>0.1234713449877366</v>
+        <v>0.1186234085776494</v>
       </c>
       <c r="F20">
-        <v>0.1135439279414511</v>
+        <v>0.1116226418764622</v>
       </c>
       <c r="G20">
-        <v>0.1242997117706587</v>
+        <v>0.12076514232656869</v>
       </c>
       <c r="H20">
-        <v>0.1421706082531371</v>
+        <v>0.13942791951965741</v>
       </c>
       <c r="I20">
-        <v>0.18048497755003651</v>
+        <v>0.17574463063684839</v>
       </c>
       <c r="J20">
-        <v>0.21873072231679469</v>
+        <v>0.21514225953277491</v>
       </c>
       <c r="K20">
-        <v>0.24858503057411199</v>
+        <v>0.24352703281597851</v>
       </c>
       <c r="L20">
-        <v>0.28611672269325178</v>
+        <v>0.28353530271551741</v>
       </c>
       <c r="M20">
-        <v>0.31386285739798869</v>
+        <v>0.30838929471540022</v>
       </c>
       <c r="N20">
-        <v>0.33880969797357091</v>
+        <v>0.33098232813854461</v>
       </c>
       <c r="O20">
-        <v>0.39204434692670548</v>
+        <v>0.38006597852587792</v>
       </c>
       <c r="P20">
-        <v>0.45168571610307789</v>
+        <v>0.44413823703681071</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -1628,49 +1588,49 @@
         <v>35</v>
       </c>
       <c r="B21">
-        <v>4.0383848795315702E-2</v>
+        <v>3.7936931166678567E-2</v>
       </c>
       <c r="C21">
-        <v>4.1083583077589247E-2</v>
+        <v>4.0803992721457127E-2</v>
       </c>
       <c r="D21">
-        <v>7.2654652500202532E-2</v>
+        <v>7.1560568979368577E-2</v>
       </c>
       <c r="E21">
-        <v>0.1829618690251559</v>
+        <v>0.17761349139521759</v>
       </c>
       <c r="F21">
-        <v>0.15986816699865919</v>
+        <v>0.1561468082213899</v>
       </c>
       <c r="G21">
-        <v>0.2030360931577109</v>
+        <v>0.19788613000857919</v>
       </c>
       <c r="H21">
-        <v>0.30768262924241091</v>
+        <v>0.30563740578045667</v>
       </c>
       <c r="I21">
-        <v>0.36114727275135727</v>
+        <v>0.35991714107382999</v>
       </c>
       <c r="J21">
-        <v>0.3899313528355523</v>
+        <v>0.39323369772343192</v>
       </c>
       <c r="K21">
-        <v>0.44668914141548771</v>
+        <v>0.44991113748621309</v>
       </c>
       <c r="L21">
-        <v>0.493860247660448</v>
+        <v>0.50457408539890136</v>
       </c>
       <c r="M21">
-        <v>0.52885882485050228</v>
+        <v>0.53507786066356433</v>
       </c>
       <c r="N21">
-        <v>0.5587765848289864</v>
+        <v>0.5648817194986302</v>
       </c>
       <c r="O21">
-        <v>0.57315093206184886</v>
+        <v>0.58221980765181269</v>
       </c>
       <c r="P21">
-        <v>0.6047453204143467</v>
+        <v>0.61109571032181664</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -1678,49 +1638,49 @@
         <v>36</v>
       </c>
       <c r="B22">
-        <v>4.207849338959696E-2</v>
+        <v>4.5149744853845257E-2</v>
       </c>
       <c r="C22">
-        <v>4.3396991472577313E-2</v>
+        <v>4.1822133483327813E-2</v>
       </c>
       <c r="D22">
-        <v>7.3064103268117131E-2</v>
+        <v>7.1221172801209764E-2</v>
       </c>
       <c r="E22">
-        <v>0.19003391665092809</v>
+        <v>0.19000670877694589</v>
       </c>
       <c r="F22">
-        <v>0.15672313918487679</v>
+        <v>0.1568934202179203</v>
       </c>
       <c r="G22">
-        <v>0.18834621243528449</v>
+        <v>0.18710802860308609</v>
       </c>
       <c r="H22">
-        <v>0.29020599297593458</v>
+        <v>0.29173518839796803</v>
       </c>
       <c r="I22">
-        <v>0.35105295292031707</v>
+        <v>0.3509436093800668</v>
       </c>
       <c r="J22">
-        <v>0.42536368805691471</v>
+        <v>0.41945229522668692</v>
       </c>
       <c r="K22">
-        <v>0.45115336425469488</v>
+        <v>0.44641836759529541</v>
       </c>
       <c r="L22">
-        <v>0.50644735167114852</v>
+        <v>0.50341681323574805</v>
       </c>
       <c r="M22">
-        <v>0.54164465724450439</v>
+        <v>0.54320113689045069</v>
       </c>
       <c r="N22">
-        <v>0.54837478354689084</v>
+        <v>0.5536896667886384</v>
       </c>
       <c r="O22">
-        <v>0.5555249476535904</v>
+        <v>0.56609020852791825</v>
       </c>
       <c r="P22">
-        <v>0.60689876072592197</v>
+        <v>0.61681475045954692</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -1728,49 +1688,49 @@
         <v>37</v>
       </c>
       <c r="B23">
-        <v>2.9585713630627061E-2</v>
+        <v>2.898345365394411E-2</v>
       </c>
       <c r="C23">
-        <v>4.634514843875126E-2</v>
+        <v>4.4065843975964247E-2</v>
       </c>
       <c r="D23">
-        <v>9.8566106433042922E-2</v>
+        <v>9.2246568057160916E-2</v>
       </c>
       <c r="E23">
-        <v>0.10149884755385651</v>
+        <v>9.3900157343097979E-2</v>
       </c>
       <c r="F23">
-        <v>0.2229785733785363</v>
+        <v>0.2101004004518025</v>
       </c>
       <c r="G23">
-        <v>0.25015914740724432</v>
+        <v>0.2427469158245428</v>
       </c>
       <c r="H23">
-        <v>0.36361219486296642</v>
+        <v>0.35527927741342769</v>
       </c>
       <c r="I23">
-        <v>0.42571546094907059</v>
+        <v>0.42293227192842481</v>
       </c>
       <c r="J23">
-        <v>0.45410526143249069</v>
+        <v>0.44950544861303399</v>
       </c>
       <c r="K23">
-        <v>0.50765775445986161</v>
+        <v>0.50383867753390699</v>
       </c>
       <c r="L23">
-        <v>0.58332901022422168</v>
+        <v>0.57903605986981455</v>
       </c>
       <c r="M23">
-        <v>0.65520499919828445</v>
+        <v>0.6489700119158256</v>
       </c>
       <c r="N23">
-        <v>0.7119235360287568</v>
+        <v>0.70915338404899142</v>
       </c>
       <c r="O23">
-        <v>0.73792055678213719</v>
+        <v>0.72925940646389087</v>
       </c>
       <c r="P23">
-        <v>0.79997566108529339</v>
+        <v>0.79001243076792882</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -1778,49 +1738,49 @@
         <v>38</v>
       </c>
       <c r="B24">
-        <v>5.5457248952103438E-2</v>
+        <v>2.81830793101745E-2</v>
       </c>
       <c r="C24">
-        <v>0.1238279185323484</v>
+        <v>4.6106462681803073E-2</v>
       </c>
       <c r="D24">
-        <v>0.14291983384331461</v>
+        <v>8.6506738515882309E-2</v>
       </c>
       <c r="E24">
-        <v>0.19496748539154041</v>
+        <v>8.5819398551050363E-2</v>
       </c>
       <c r="F24">
-        <v>0.44696558092695388</v>
+        <v>0.1038449141088208</v>
       </c>
       <c r="G24">
-        <v>0.41286041611114621</v>
+        <v>0.101951618458844</v>
       </c>
       <c r="H24">
-        <v>0.4767563330711157</v>
+        <v>0.1222874986219228</v>
       </c>
       <c r="I24">
-        <v>0.62547209494722311</v>
+        <v>0.14668442199663351</v>
       </c>
       <c r="J24">
-        <v>0.73777029466863686</v>
+        <v>0.18996344368488399</v>
       </c>
       <c r="K24">
-        <v>0.80993310459546464</v>
+        <v>0.25052069616515099</v>
       </c>
       <c r="L24">
-        <v>0.86610524322914162</v>
+        <v>0.32130447904722059</v>
       </c>
       <c r="M24">
-        <v>0.93971680665214197</v>
+        <v>0.43001467719563219</v>
       </c>
       <c r="N24">
-        <v>1.012153058822638</v>
+        <v>0.4749981164057635</v>
       </c>
       <c r="O24">
-        <v>1.0838918089716341</v>
+        <v>0.52838993627825848</v>
       </c>
       <c r="P24">
-        <v>1.1197720950151411</v>
+        <v>0.57424494179609975</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -1828,49 +1788,49 @@
         <v>39</v>
       </c>
       <c r="B25">
-        <v>7.3130170593493943E-2</v>
+        <v>2.5249193007567779E-2</v>
       </c>
       <c r="C25">
-        <v>0.1296269406831394</v>
+        <v>4.4423771234235583E-2</v>
       </c>
       <c r="D25">
-        <v>0.1637336129746369</v>
+        <v>9.0735552519235485E-2</v>
       </c>
       <c r="E25">
-        <v>0.26292168230693552</v>
+        <v>8.5930812636035303E-2</v>
       </c>
       <c r="F25">
-        <v>0.33578133987769598</v>
+        <v>0.1124854535257853</v>
       </c>
       <c r="G25">
-        <v>0.4286745254917792</v>
+        <v>0.1175054304208648</v>
       </c>
       <c r="H25">
-        <v>0.54888097901732724</v>
+        <v>0.13533973040443029</v>
       </c>
       <c r="I25">
-        <v>0.66751816294408073</v>
+        <v>0.18856751620933079</v>
       </c>
       <c r="J25">
-        <v>0.82242092068006578</v>
+        <v>0.17817191252365891</v>
       </c>
       <c r="K25">
-        <v>0.98263077126098186</v>
+        <v>0.22133449818300621</v>
       </c>
       <c r="L25">
-        <v>1.1296023027475</v>
+        <v>0.29034512908158011</v>
       </c>
       <c r="M25">
-        <v>1.2434241949995231</v>
+        <v>0.33369577532392508</v>
       </c>
       <c r="N25">
-        <v>1.3095774102784381</v>
+        <v>0.42987695446607083</v>
       </c>
       <c r="O25">
-        <v>1.3773825176812511</v>
+        <v>0.47198132754174449</v>
       </c>
       <c r="P25">
-        <v>1.423233234222437</v>
+        <v>0.51055988955477982</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -1878,49 +1838,49 @@
         <v>40</v>
       </c>
       <c r="B26">
-        <v>5.2473605458558607E-2</v>
+        <v>2.6970685049099611E-2</v>
       </c>
       <c r="C26">
-        <v>0.1184645580887284</v>
+        <v>4.8534588963266352E-2</v>
       </c>
       <c r="D26">
-        <v>0.1074103607115426</v>
+        <v>0.11569400053800361</v>
       </c>
       <c r="E26">
-        <v>0.14619607857831399</v>
+        <v>9.6670425771907098E-2</v>
       </c>
       <c r="F26">
-        <v>0.31358405443272669</v>
+        <v>0.1168253695988621</v>
       </c>
       <c r="G26">
-        <v>0.35056746978774878</v>
+        <v>0.1066844311311245</v>
       </c>
       <c r="H26">
-        <v>0.42756560332833171</v>
+        <v>0.1148507662203589</v>
       </c>
       <c r="I26">
-        <v>0.49376376609956257</v>
+        <v>0.14567587713592561</v>
       </c>
       <c r="J26">
-        <v>0.45671490374320928</v>
+        <v>0.2229421710837132</v>
       </c>
       <c r="K26">
-        <v>0.54077426697211017</v>
+        <v>0.26815422004865103</v>
       </c>
       <c r="L26">
-        <v>0.64344321425006656</v>
+        <v>0.34674837775976991</v>
       </c>
       <c r="M26">
-        <v>0.78046342941721236</v>
+        <v>0.42495116839360703</v>
       </c>
       <c r="N26">
-        <v>0.86191240405506908</v>
+        <v>0.45422762453350318</v>
       </c>
       <c r="O26">
-        <v>0.90545761385194101</v>
+        <v>0.510737587363159</v>
       </c>
       <c r="P26">
-        <v>0.98706329486858924</v>
+        <v>0.5598010716652364</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -1928,49 +1888,49 @@
         <v>41</v>
       </c>
       <c r="B27">
-        <v>6.0379130150355717E-2</v>
+        <v>2.5155635671524901E-2</v>
       </c>
       <c r="C27">
-        <v>9.2311223204041587E-2</v>
+        <v>4.6225230055635953E-2</v>
       </c>
       <c r="D27">
-        <v>0.2208162666179786</v>
+        <v>0.1122910520841999</v>
       </c>
       <c r="E27">
-        <v>0.1854896445463329</v>
+        <v>9.0890449124327866E-2</v>
       </c>
       <c r="F27">
-        <v>0.29672788093297192</v>
+        <v>0.11359768459250261</v>
       </c>
       <c r="G27">
-        <v>0.4043973078872376</v>
+        <v>9.9294360138136306E-2</v>
       </c>
       <c r="H27">
-        <v>0.43989639289959259</v>
+        <v>0.10259048222277201</v>
       </c>
       <c r="I27">
-        <v>0.54400535953422591</v>
+        <v>0.1165954988606662</v>
       </c>
       <c r="J27">
-        <v>0.73489083301792235</v>
+        <v>0.15275719469227489</v>
       </c>
       <c r="K27">
-        <v>0.82068013737949264</v>
+        <v>0.1636407974810731</v>
       </c>
       <c r="L27">
-        <v>0.89800535089945477</v>
+        <v>0.18934022375227549</v>
       </c>
       <c r="M27">
-        <v>1.041876919468786</v>
+        <v>0.25810523585363437</v>
       </c>
       <c r="N27">
-        <v>1.0361133978421611</v>
+        <v>0.27336334242982269</v>
       </c>
       <c r="O27">
-        <v>1.137087238634638</v>
+        <v>0.31341593140952367</v>
       </c>
       <c r="P27">
-        <v>1.193686279000302</v>
+        <v>0.33977646269755651</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -1978,49 +1938,49 @@
         <v>42</v>
       </c>
       <c r="B28">
-        <v>2.7471527437007089E-2</v>
+        <v>2.454469045521079E-2</v>
       </c>
       <c r="C28">
-        <v>4.5592847904726057E-2</v>
+        <v>4.1612411880071143E-2</v>
       </c>
       <c r="D28">
-        <v>8.974341420149945E-2</v>
+        <v>8.9967211713680606E-2</v>
       </c>
       <c r="E28">
-        <v>8.6415499892448677E-2</v>
+        <v>8.4492678088170292E-2</v>
       </c>
       <c r="F28">
-        <v>0.1071042362104377</v>
+        <v>0.10559411792721821</v>
       </c>
       <c r="G28">
-        <v>0.1057478301179741</v>
+        <v>0.1055521919800594</v>
       </c>
       <c r="H28">
-        <v>0.12280194636115351</v>
+        <v>0.1175700382263157</v>
       </c>
       <c r="I28">
-        <v>0.1487623634385126</v>
+        <v>0.14776175820179219</v>
       </c>
       <c r="J28">
-        <v>0.19088402401864379</v>
+        <v>0.13199190284275811</v>
       </c>
       <c r="K28">
-        <v>0.2537201612991471</v>
+        <v>0.14436150721801561</v>
       </c>
       <c r="L28">
-        <v>0.32194412676000328</v>
+        <v>0.17235627850649421</v>
       </c>
       <c r="M28">
-        <v>0.42823876770467439</v>
+        <v>0.18299113231808831</v>
       </c>
       <c r="N28">
-        <v>0.47323866372111018</v>
+        <v>0.2209521844388429</v>
       </c>
       <c r="O28">
-        <v>0.52544119736913331</v>
+        <v>0.24409611597811301</v>
       </c>
       <c r="P28">
-        <v>0.56790734715064728</v>
+        <v>0.30744553725149532</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2028,49 +1988,49 @@
         <v>43</v>
       </c>
       <c r="B29">
-        <v>2.7176370737333699E-2</v>
+        <v>2.6593569202518989E-2</v>
       </c>
       <c r="C29">
-        <v>4.5221082759714037E-2</v>
+        <v>4.4319643840832423E-2</v>
       </c>
       <c r="D29">
-        <v>9.3139445940101262E-2</v>
+        <v>8.9983640223392336E-2</v>
       </c>
       <c r="E29">
-        <v>8.7538373326920271E-2</v>
+        <v>8.6937488880439728E-2</v>
       </c>
       <c r="F29">
-        <v>0.11251605973320609</v>
+        <v>0.1104398337722228</v>
       </c>
       <c r="G29">
-        <v>0.11413788753727221</v>
+        <v>0.11121643148370799</v>
       </c>
       <c r="H29">
-        <v>0.13663843606658041</v>
+        <v>0.12436550770928589</v>
       </c>
       <c r="I29">
-        <v>0.1858421074268797</v>
+        <v>0.15128142427258931</v>
       </c>
       <c r="J29">
-        <v>0.1727454010148175</v>
+        <v>0.13820709767607781</v>
       </c>
       <c r="K29">
-        <v>0.21981830463862409</v>
+        <v>0.14599172529457341</v>
       </c>
       <c r="L29">
-        <v>0.28864391219209612</v>
+        <v>0.17210844712169759</v>
       </c>
       <c r="M29">
-        <v>0.3294940118173405</v>
+        <v>0.181045448647738</v>
       </c>
       <c r="N29">
-        <v>0.42600724078415569</v>
+        <v>0.21092337808855191</v>
       </c>
       <c r="O29">
-        <v>0.46460458911465119</v>
+        <v>0.22727643774886661</v>
       </c>
       <c r="P29">
-        <v>0.50095373711234314</v>
+        <v>0.28424305633630842</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2078,49 +2038,49 @@
         <v>44</v>
       </c>
       <c r="B30">
-        <v>2.5062210131161059E-2</v>
+        <v>2.5866336241035959E-2</v>
       </c>
       <c r="C30">
-        <v>4.4498994438358142E-2</v>
+        <v>4.342022951704505E-2</v>
       </c>
       <c r="D30">
-        <v>0.10798695921799591</v>
+        <v>8.7354665805358556E-2</v>
       </c>
       <c r="E30">
-        <v>9.7345553965398013E-2</v>
+        <v>8.3855643374616484E-2</v>
       </c>
       <c r="F30">
-        <v>0.1180429698585673</v>
+        <v>0.10783679263960071</v>
       </c>
       <c r="G30">
-        <v>0.10825067161960231</v>
+        <v>0.1085298406810985</v>
       </c>
       <c r="H30">
-        <v>0.1177524192833292</v>
+        <v>0.1235399814433138</v>
       </c>
       <c r="I30">
-        <v>0.15059910586843769</v>
+        <v>0.15028358485342641</v>
       </c>
       <c r="J30">
-        <v>0.22986346274803759</v>
+        <v>0.13797467689434459</v>
       </c>
       <c r="K30">
-        <v>0.27266000476001689</v>
+        <v>0.1415586477146116</v>
       </c>
       <c r="L30">
-        <v>0.34901710857638302</v>
+        <v>0.16995431166546551</v>
       </c>
       <c r="M30">
-        <v>0.43118295538591639</v>
+        <v>0.1777355295390676</v>
       </c>
       <c r="N30">
-        <v>0.46104433323963168</v>
+        <v>0.20407853902827941</v>
       </c>
       <c r="O30">
-        <v>0.51555938209167884</v>
+        <v>0.21809335558017651</v>
       </c>
       <c r="P30">
-        <v>0.56389005204837828</v>
+        <v>0.27240551549730913</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2128,49 +2088,49 @@
         <v>45</v>
       </c>
       <c r="B31">
-        <v>2.224786142616442E-2</v>
+        <v>2.706670091448116E-2</v>
       </c>
       <c r="C31">
-        <v>4.3293496916469547E-2</v>
+        <v>4.5657890617050827E-2</v>
       </c>
       <c r="D31">
-        <v>0.11007579934623279</v>
+        <v>9.1804513190871573E-2</v>
       </c>
       <c r="E31">
-        <v>9.2118323308021943E-2</v>
+        <v>8.6474099369967083E-2</v>
       </c>
       <c r="F31">
-        <v>0.1117493687440463</v>
+        <v>0.1083789766618363</v>
       </c>
       <c r="G31">
-        <v>9.9664953152933666E-2</v>
+        <v>0.1102124533851879</v>
       </c>
       <c r="H31">
-        <v>0.1018875940982443</v>
+        <v>0.1229900944630555</v>
       </c>
       <c r="I31">
-        <v>0.1154505184070851</v>
+        <v>0.14857383360082091</v>
       </c>
       <c r="J31">
-        <v>0.15280149455843819</v>
+        <v>0.13927566569408881</v>
       </c>
       <c r="K31">
-        <v>0.1646701519904461</v>
+        <v>0.14107712249029891</v>
       </c>
       <c r="L31">
-        <v>0.19019227663843649</v>
+        <v>0.16645902994505321</v>
       </c>
       <c r="M31">
-        <v>0.26002907950441612</v>
+        <v>0.17112602616748659</v>
       </c>
       <c r="N31">
-        <v>0.27598165790016949</v>
+        <v>0.19473586071962309</v>
       </c>
       <c r="O31">
-        <v>0.31716991564256553</v>
+        <v>0.20692417867894031</v>
       </c>
       <c r="P31">
-        <v>0.3463363629794361</v>
+        <v>0.2525591361974372</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2178,49 +2138,49 @@
         <v>46</v>
       </c>
       <c r="B32">
-        <v>2.557469415750491E-2</v>
+        <v>2.7504286522712751E-2</v>
       </c>
       <c r="C32">
-        <v>4.1924504724844318E-2</v>
+        <v>4.5249321715328361E-2</v>
       </c>
       <c r="D32">
-        <v>8.4723205098630849E-2</v>
+        <v>9.407355876725354E-2</v>
       </c>
       <c r="E32">
-        <v>8.1631785876995933E-2</v>
+        <v>8.3712995103220278E-2</v>
       </c>
       <c r="F32">
-        <v>0.1048503069930313</v>
+        <v>0.10913991631748431</v>
       </c>
       <c r="G32">
-        <v>0.1057887712663037</v>
+        <v>0.1130555985882971</v>
       </c>
       <c r="H32">
-        <v>0.1193996916322944</v>
+        <v>0.12597374620357379</v>
       </c>
       <c r="I32">
-        <v>0.14669012815181781</v>
+        <v>0.15928702797543609</v>
       </c>
       <c r="J32">
-        <v>0.1333091619670026</v>
-      </c>
-      <c r="K32" s="2">
-        <v>0.14149736870708421</v>
+        <v>0.142750650380053</v>
+      </c>
+      <c r="K32">
+        <v>0.15547409185808689</v>
       </c>
       <c r="L32">
-        <v>0.1692256235947511</v>
+        <v>0.19739864934106111</v>
       </c>
       <c r="M32">
-        <v>0.17851324284974041</v>
+        <v>0.20706790573125339</v>
       </c>
       <c r="N32">
-        <v>0.21548778879401709</v>
+        <v>0.2619419584312368</v>
       </c>
       <c r="O32">
-        <v>0.23554996195898861</v>
+        <v>0.27850818600966382</v>
       </c>
       <c r="P32">
-        <v>0.29627690165930592</v>
+        <v>0.32373218508982182</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2228,49 +2188,49 @@
         <v>47</v>
       </c>
       <c r="B33">
-        <v>2.7820068789040309E-2</v>
+        <v>2.8041719537179599E-2</v>
       </c>
       <c r="C33">
-        <v>4.5086129796523933E-2</v>
+        <v>4.5784718639044319E-2</v>
       </c>
       <c r="D33">
-        <v>8.8265128314120589E-2</v>
+        <v>8.9482332911895668E-2</v>
       </c>
       <c r="E33">
-        <v>8.3204607640049E-2</v>
+        <v>8.5841737449277034E-2</v>
       </c>
       <c r="F33">
-        <v>0.10683298331412761</v>
+        <v>0.1080453372990391</v>
       </c>
       <c r="G33">
-        <v>0.1078397955880456</v>
+        <v>0.1117492006095795</v>
       </c>
       <c r="H33">
-        <v>0.11913835404924709</v>
+        <v>0.122111416860023</v>
       </c>
       <c r="I33">
-        <v>0.15181964877399171</v>
+        <v>0.1550870105893403</v>
       </c>
       <c r="J33">
-        <v>0.1414143233861902</v>
+        <v>0.14104670414309689</v>
       </c>
       <c r="K33">
-        <v>0.14436123545510729</v>
+        <v>0.1551337677533435</v>
       </c>
       <c r="L33">
-        <v>0.1733762028904334</v>
+        <v>0.18969551891405331</v>
       </c>
       <c r="M33">
-        <v>0.18290368317586611</v>
+        <v>0.19989214422166579</v>
       </c>
       <c r="N33">
-        <v>0.21499680633921001</v>
+        <v>0.25354974980998829</v>
       </c>
       <c r="O33">
-        <v>0.23129976597332269</v>
+        <v>0.2641153013534554</v>
       </c>
       <c r="P33">
-        <v>0.29145797604750201</v>
+        <v>0.31023480850627222</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2278,49 +2238,49 @@
         <v>48</v>
       </c>
       <c r="B34">
-        <v>2.7816601286415499E-2</v>
+        <v>2.8407194245906431E-2</v>
       </c>
       <c r="C34">
-        <v>4.4720593872889403E-2</v>
+        <v>4.5511978076475217E-2</v>
       </c>
       <c r="D34">
-        <v>8.8807919491984855E-2</v>
+        <v>8.724569702036955E-2</v>
       </c>
       <c r="E34">
-        <v>8.4899725728792119E-2</v>
+        <v>8.782314712616146E-2</v>
       </c>
       <c r="F34">
-        <v>0.1102064674306884</v>
+        <v>0.1108525490217088</v>
       </c>
       <c r="G34">
-        <v>0.11049485538919659</v>
+        <v>0.11493066887088289</v>
       </c>
       <c r="H34">
-        <v>0.1232859155565665</v>
+        <v>0.1287074674766624</v>
       </c>
       <c r="I34">
-        <v>0.1484957117746106</v>
+        <v>0.15990116783641259</v>
       </c>
       <c r="J34">
-        <v>0.13874396391373781</v>
+        <v>0.14220865941341859</v>
       </c>
       <c r="K34">
-        <v>0.1483845809015075</v>
+        <v>0.15697352057333069</v>
       </c>
       <c r="L34">
-        <v>0.17089000120234579</v>
+        <v>0.18765030564860641</v>
       </c>
       <c r="M34">
-        <v>0.17817130777858381</v>
+        <v>0.19798990031512981</v>
       </c>
       <c r="N34">
-        <v>0.2048107111845052</v>
+        <v>0.2489750634121719</v>
       </c>
       <c r="O34">
-        <v>0.21829390900102541</v>
+        <v>0.25573942913989228</v>
       </c>
       <c r="P34">
-        <v>0.27156542786416471</v>
+        <v>0.29384010659319532</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2328,49 +2288,49 @@
         <v>49</v>
       </c>
       <c r="B35">
-        <v>2.7352327571632199E-2</v>
+        <v>2.7168574120662089E-2</v>
       </c>
       <c r="C35">
-        <v>4.4935175372075482E-2</v>
+        <v>4.3121352039615091E-2</v>
       </c>
       <c r="D35">
-        <v>9.0974659813742642E-2</v>
+        <v>8.412196443868325E-2</v>
       </c>
       <c r="E35">
-        <v>8.2907008510337166E-2</v>
+        <v>8.2199797444934553E-2</v>
       </c>
       <c r="F35">
-        <v>0.10542718270298231</v>
+        <v>0.1050599065655634</v>
       </c>
       <c r="G35">
-        <v>0.106833469640375</v>
+        <v>0.104190506225376</v>
       </c>
       <c r="H35">
-        <v>0.1185244352904521</v>
+        <v>0.1169836481086841</v>
       </c>
       <c r="I35">
-        <v>0.14328988365563139</v>
+        <v>0.14444620368144831</v>
       </c>
       <c r="J35">
-        <v>0.13533505397917239</v>
+        <v>0.13126372129387481</v>
       </c>
       <c r="K35">
-        <v>0.13986751425505431</v>
+        <v>0.14232979252192651</v>
       </c>
       <c r="L35">
-        <v>0.1631353283756658</v>
+        <v>0.1691217010403773</v>
       </c>
       <c r="M35">
-        <v>0.1676602093209012</v>
+        <v>0.18000522273919761</v>
       </c>
       <c r="N35">
-        <v>0.18960559078951639</v>
+        <v>0.23232390594850991</v>
       </c>
       <c r="O35">
-        <v>0.20089455529953179</v>
+        <v>0.24457732178705169</v>
       </c>
       <c r="P35">
-        <v>0.24351001322556209</v>
+        <v>0.28634598629109281</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2378,49 +2338,49 @@
         <v>50</v>
       </c>
       <c r="B36">
-        <v>2.5743007746458099E-2</v>
+        <v>2.666433162291271E-2</v>
       </c>
       <c r="C36">
-        <v>4.2589952371352657E-2</v>
+        <v>4.4319894301593998E-2</v>
       </c>
       <c r="D36">
-        <v>8.5903322809944616E-2</v>
+        <v>8.8800161069937267E-2</v>
       </c>
       <c r="E36">
-        <v>8.0741025934952249E-2</v>
+        <v>8.2568029543353627E-2</v>
       </c>
       <c r="F36">
-        <v>0.10533800049244139</v>
+        <v>0.1073352207447297</v>
       </c>
       <c r="G36">
-        <v>0.10708294433766199</v>
+        <v>0.1094909714801028</v>
       </c>
       <c r="H36">
-        <v>0.1188168199986321</v>
+        <v>0.12115421657223931</v>
       </c>
       <c r="I36">
-        <v>0.15356637080823671</v>
+        <v>0.1472303658874872</v>
       </c>
       <c r="J36">
-        <v>0.13612437680184161</v>
+        <v>0.13615139842391261</v>
       </c>
       <c r="K36">
-        <v>0.1522473525814225</v>
+        <v>0.14128413188742889</v>
       </c>
       <c r="L36">
-        <v>0.18655419929977909</v>
+        <v>0.1671772809020633</v>
       </c>
       <c r="M36">
-        <v>0.19441872757150611</v>
+        <v>0.17381483822569899</v>
       </c>
       <c r="N36">
-        <v>0.25064855377459971</v>
+        <v>0.2027454475925409</v>
       </c>
       <c r="O36">
-        <v>0.26465229778529109</v>
+        <v>0.21752370083277811</v>
       </c>
       <c r="P36">
-        <v>0.3097658333186496</v>
+        <v>0.25803719496109678</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2428,49 +2388,49 @@
         <v>51</v>
       </c>
       <c r="B37">
-        <v>2.6546600948498481E-2</v>
+        <v>2.433597668854048E-2</v>
       </c>
       <c r="C37">
-        <v>4.2913586230744483E-2</v>
+        <v>4.5665496466244071E-2</v>
       </c>
       <c r="D37">
-        <v>8.3031713270249385E-2</v>
+        <v>9.8229804092664685E-2</v>
       </c>
       <c r="E37">
-        <v>8.0106244222305611E-2</v>
+        <v>0.11782372505419279</v>
       </c>
       <c r="F37">
-        <v>0.1033345168535966</v>
+        <v>0.21000994372370141</v>
       </c>
       <c r="G37">
-        <v>0.10532205830786601</v>
+        <v>0.28292570341428802</v>
       </c>
       <c r="H37">
-        <v>0.12110462087211341</v>
+        <v>0.27156100120135579</v>
       </c>
       <c r="I37">
-        <v>0.14922573183537269</v>
+        <v>0.30567347385062998</v>
       </c>
       <c r="J37">
-        <v>0.13624910552754629</v>
+        <v>0.34176961066206402</v>
       </c>
       <c r="K37">
-        <v>0.14941449989701841</v>
+        <v>0.40459147755223218</v>
       </c>
       <c r="L37">
-        <v>0.18400578826494041</v>
+        <v>0.42096745089106441</v>
       </c>
       <c r="M37">
-        <v>0.19328517577593141</v>
+        <v>0.44935875298664368</v>
       </c>
       <c r="N37">
-        <v>0.24499994063444819</v>
+        <v>0.51091763684622193</v>
       </c>
       <c r="O37">
-        <v>0.25797005241789789</v>
+        <v>0.57342893410605877</v>
       </c>
       <c r="P37">
-        <v>0.30365384287252889</v>
+        <v>0.60865567186718306</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2478,49 +2438,49 @@
         <v>52</v>
       </c>
       <c r="B38">
-        <v>2.4632687010503921E-2</v>
+        <v>2.6731329636889511E-2</v>
       </c>
       <c r="C38">
-        <v>4.1511052355642668E-2</v>
+        <v>4.2392453292670502E-2</v>
       </c>
       <c r="D38">
-        <v>8.5546688507448176E-2</v>
+        <v>8.2347868617622888E-2</v>
       </c>
       <c r="E38">
-        <v>7.8117111523870353E-2</v>
+        <v>9.4571239646587868E-2</v>
       </c>
       <c r="F38">
-        <v>0.10353282545172331</v>
+        <v>0.14934763057646899</v>
       </c>
       <c r="G38">
-        <v>0.1058392791634378</v>
+        <v>0.19539603279694939</v>
       </c>
       <c r="H38">
-        <v>0.11791296875136729</v>
+        <v>0.17622216648679229</v>
       </c>
       <c r="I38">
-        <v>0.14743557507251329</v>
+        <v>0.23174691773930309</v>
       </c>
       <c r="J38">
-        <v>0.13526668071292869</v>
+        <v>0.27845596726000332</v>
       </c>
       <c r="K38">
-        <v>0.1478762853218599</v>
+        <v>0.32835843293208911</v>
       </c>
       <c r="L38">
-        <v>0.1801165450946263</v>
+        <v>0.32788169026205038</v>
       </c>
       <c r="M38">
-        <v>0.1875187956823571</v>
+        <v>0.34176758313948158</v>
       </c>
       <c r="N38">
-        <v>0.2387250522584338</v>
+        <v>0.37932496675126182</v>
       </c>
       <c r="O38">
-        <v>0.24979617440515339</v>
+        <v>0.42529573203889459</v>
       </c>
       <c r="P38">
-        <v>0.28881220394923202</v>
+        <v>0.42471491891699542</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -2528,49 +2488,49 @@
         <v>53</v>
       </c>
       <c r="B39">
-        <v>2.6465972821027139E-2</v>
+        <v>2.822617041305386E-2</v>
       </c>
       <c r="C39">
-        <v>4.4456809849829249E-2</v>
+        <v>4.3073624751423727E-2</v>
       </c>
       <c r="D39">
-        <v>8.8552174814998108E-2</v>
+        <v>7.6907709423450932E-2</v>
       </c>
       <c r="E39">
-        <v>8.8206194256563841E-2</v>
+        <v>8.5274536956821412E-2</v>
       </c>
       <c r="F39">
-        <v>0.1094393166281156</v>
+        <v>0.12590314171038169</v>
       </c>
       <c r="G39">
-        <v>0.1100724839112613</v>
+        <v>0.15969851948599961</v>
       </c>
       <c r="H39">
-        <v>0.12621096917449631</v>
+        <v>0.14161099970664401</v>
       </c>
       <c r="I39">
-        <v>0.1525414538192148</v>
+        <v>0.17564919034005019</v>
       </c>
       <c r="J39">
-        <v>0.1387091388152468</v>
+        <v>0.26067916475495567</v>
       </c>
       <c r="K39">
-        <v>0.14844222852986591</v>
+        <v>0.26913115976100122</v>
       </c>
       <c r="L39">
-        <v>0.1800453943952651</v>
+        <v>0.29341050170436378</v>
       </c>
       <c r="M39">
-        <v>0.19093599780883561</v>
+        <v>0.31833693732545648</v>
       </c>
       <c r="N39">
-        <v>0.24271714502910799</v>
+        <v>0.37590270254686903</v>
       </c>
       <c r="O39">
-        <v>0.25299551479715909</v>
+        <v>0.41435063148002771</v>
       </c>
       <c r="P39">
-        <v>0.29283907251590041</v>
+        <v>0.48023890000893482</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -2578,49 +2538,49 @@
         <v>54</v>
       </c>
       <c r="B40">
-        <v>2.7405237553673519E-2</v>
+        <v>2.7557925478080229E-2</v>
       </c>
       <c r="C40">
-        <v>4.3957073831793259E-2</v>
+        <v>4.8788302908161052E-2</v>
       </c>
       <c r="D40">
-        <v>8.6372921722166707E-2</v>
+        <v>6.1450503159405701E-2</v>
       </c>
       <c r="E40">
-        <v>8.5393308185334305E-2</v>
+        <v>0.11084873482699741</v>
       </c>
       <c r="F40">
-        <v>0.1060443419703736</v>
+        <v>0.15078730808526891</v>
       </c>
       <c r="G40">
-        <v>0.10813090645387841</v>
+        <v>0.21595765447256679</v>
       </c>
       <c r="H40">
-        <v>0.1200959823070072</v>
+        <v>0.32852167103778951</v>
       </c>
       <c r="I40">
-        <v>0.1499383196626787</v>
+        <v>0.38233390014560309</v>
       </c>
       <c r="J40">
-        <v>0.1391328033370991</v>
+        <v>0.44610245387555902</v>
       </c>
       <c r="K40">
-        <v>0.1445221600345212</v>
+        <v>0.50394905499127818</v>
       </c>
       <c r="L40">
-        <v>0.16923479862437471</v>
+        <v>0.59556857442075473</v>
       </c>
       <c r="M40">
-        <v>0.1763069664300885</v>
+        <v>0.71858245933998011</v>
       </c>
       <c r="N40">
-        <v>0.20555768414906661</v>
+        <v>0.87996410471204367</v>
       </c>
       <c r="O40">
-        <v>0.21865023338808279</v>
+        <v>0.99632918534691639</v>
       </c>
       <c r="P40">
-        <v>0.26341403287780402</v>
+        <v>1.0404115957595541</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -2628,49 +2588,49 @@
         <v>55</v>
       </c>
       <c r="B41">
-        <v>2.470607486247722E-2</v>
+        <v>4.2948083670724557E-2</v>
       </c>
       <c r="C41">
-        <v>4.6491249958536041E-2</v>
+        <v>6.3524369480308596E-2</v>
       </c>
       <c r="D41">
-        <v>0.10180813667997141</v>
+        <v>0.14501881335244929</v>
       </c>
       <c r="E41">
-        <v>0.1235051412725682</v>
+        <v>0.26553021143556099</v>
       </c>
       <c r="F41">
-        <v>0.21658869673242001</v>
+        <v>0.37584796846632612</v>
       </c>
       <c r="G41">
-        <v>0.2925473323118159</v>
+        <v>0.41289532840781229</v>
       </c>
       <c r="H41">
-        <v>0.27710070074731841</v>
+        <v>0.46694811326055657</v>
       </c>
       <c r="I41">
-        <v>0.31385603524533301</v>
+        <v>0.48776223752542208</v>
       </c>
       <c r="J41">
-        <v>0.35273981559247031</v>
+        <v>0.50917371013470414</v>
       </c>
       <c r="K41">
-        <v>0.41576464678508551</v>
+        <v>0.54076857116934596</v>
       </c>
       <c r="L41">
-        <v>0.42704745246591758</v>
+        <v>0.59054927082588327</v>
       </c>
       <c r="M41">
-        <v>0.4549258509104564</v>
+        <v>0.68378369864211352</v>
       </c>
       <c r="N41">
-        <v>0.51504177634370962</v>
+        <v>0.73571348582947094</v>
       </c>
       <c r="O41">
-        <v>0.56994041812211593</v>
+        <v>0.7734762015279909</v>
       </c>
       <c r="P41">
-        <v>0.6077643269576154</v>
+        <v>0.78486421587048127</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2678,49 +2638,49 @@
         <v>56</v>
       </c>
       <c r="B42">
-        <v>2.62898013259476E-2</v>
+        <v>5.0610996410996811E-2</v>
       </c>
       <c r="C42">
-        <v>4.3169552447860138E-2</v>
+        <v>4.9652744075355359E-2</v>
       </c>
       <c r="D42">
-        <v>8.1152051616948051E-2</v>
+        <v>0.11172834959077731</v>
       </c>
       <c r="E42">
-        <v>8.6415260429941743E-2</v>
+        <v>0.2241597969625313</v>
       </c>
       <c r="F42">
-        <v>0.14216418040079001</v>
+        <v>0.2350201190264527</v>
       </c>
       <c r="G42">
-        <v>0.18423387321913789</v>
+        <v>0.27460026452173009</v>
       </c>
       <c r="H42">
-        <v>0.16976233144439951</v>
+        <v>0.29975754083076162</v>
       </c>
       <c r="I42">
-        <v>0.22723894719575741</v>
+        <v>0.32761326656952983</v>
       </c>
       <c r="J42">
-        <v>0.26447852378827991</v>
+        <v>0.47626696806117891</v>
       </c>
       <c r="K42">
-        <v>0.31474688678149948</v>
+        <v>0.57949607019498606</v>
       </c>
       <c r="L42">
-        <v>0.31119603559638959</v>
+        <v>0.66258855631554237</v>
       </c>
       <c r="M42">
-        <v>0.32538664141744522</v>
+        <v>0.69335811467738806</v>
       </c>
       <c r="N42">
-        <v>0.36138830553453177</v>
+        <v>0.72003983253363568</v>
       </c>
       <c r="O42">
-        <v>0.40544185984479442</v>
+        <v>0.72118791165257234</v>
       </c>
       <c r="P42">
-        <v>0.40942242374145288</v>
+        <v>0.71765424066952577</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -2728,257 +2688,57 @@
         <v>57</v>
       </c>
       <c r="B43">
-        <v>2.4005149072500509E-2</v>
+        <v>2.9604078281788019E-2</v>
       </c>
       <c r="C43">
-        <v>3.9893225490514987E-2</v>
+        <v>9.5842294690364649E-2</v>
       </c>
       <c r="D43">
-        <v>7.2749889817959157E-2</v>
+        <v>0.13352344123521109</v>
       </c>
       <c r="E43">
-        <v>8.1932606222986815E-2</v>
+        <v>0.20297036902505999</v>
       </c>
       <c r="F43">
-        <v>0.1245025587865505</v>
+        <v>0.30525102929819808</v>
       </c>
       <c r="G43">
-        <v>0.16064583342387509</v>
+        <v>0.35264806264180898</v>
       </c>
       <c r="H43">
-        <v>0.14079097639630381</v>
+        <v>0.35840352200177789</v>
       </c>
       <c r="I43">
-        <v>0.17476594598031989</v>
+        <v>0.37291111177949821</v>
       </c>
       <c r="J43">
-        <v>0.26249123346253278</v>
+        <v>0.40895790952805888</v>
       </c>
       <c r="K43">
-        <v>0.26971207415528597</v>
+        <v>0.49621382285396731</v>
       </c>
       <c r="L43">
-        <v>0.29228789560576007</v>
+        <v>0.5463636630445915</v>
       </c>
       <c r="M43">
-        <v>0.3165258687413447</v>
+        <v>0.59032380253721839</v>
       </c>
       <c r="N43">
-        <v>0.3764869244816445</v>
+        <v>0.60939340873870385</v>
       </c>
       <c r="O43">
-        <v>0.41688979754552619</v>
+        <v>0.62777011781836056</v>
       </c>
       <c r="P43">
-        <v>0.48746015013001298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>2.9557484432314211E-2</v>
-      </c>
-      <c r="C44">
-        <v>5.0814475579357699E-2</v>
-      </c>
-      <c r="D44">
-        <v>6.4717173997929534E-2</v>
-      </c>
-      <c r="E44">
-        <v>0.11262299457499329</v>
-      </c>
-      <c r="F44">
-        <v>0.15525663816536489</v>
-      </c>
-      <c r="G44">
-        <v>0.21624293065580361</v>
-      </c>
-      <c r="H44">
-        <v>0.33084981241661948</v>
-      </c>
-      <c r="I44">
-        <v>0.38484831233204658</v>
-      </c>
-      <c r="J44">
-        <v>0.44356863753609699</v>
-      </c>
-      <c r="K44">
-        <v>0.50153332077738566</v>
-      </c>
-      <c r="L44">
-        <v>0.59548676439434001</v>
-      </c>
-      <c r="M44">
-        <v>0.71776147708839144</v>
-      </c>
-      <c r="N44">
-        <v>0.86921374135006724</v>
-      </c>
-      <c r="O44">
-        <v>0.99808327563634325</v>
-      </c>
-      <c r="P44">
-        <v>1.032898972767256</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>4.1994450743362832E-2</v>
-      </c>
-      <c r="C45">
-        <v>6.3544354324684971E-2</v>
-      </c>
-      <c r="D45">
-        <v>0.14405923919898969</v>
-      </c>
-      <c r="E45">
-        <v>0.27007307759127641</v>
-      </c>
-      <c r="F45">
-        <v>0.382186497273382</v>
-      </c>
-      <c r="G45">
-        <v>0.42082155233260599</v>
-      </c>
-      <c r="H45">
-        <v>0.4721749599737729</v>
-      </c>
-      <c r="I45">
-        <v>0.49464722502159209</v>
-      </c>
-      <c r="J45">
-        <v>0.51686083220810386</v>
-      </c>
-      <c r="K45">
-        <v>0.55059757031461187</v>
-      </c>
-      <c r="L45">
-        <v>0.60741440333750729</v>
-      </c>
-      <c r="M45">
-        <v>0.69761235399705934</v>
-      </c>
-      <c r="N45">
-        <v>0.74382491865924294</v>
-      </c>
-      <c r="O45">
-        <v>0.78115728589953148</v>
-      </c>
-      <c r="P45">
-        <v>0.79547989029628541</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>4.6791255654761443E-2</v>
-      </c>
-      <c r="C46">
-        <v>4.692527044245981E-2</v>
-      </c>
-      <c r="D46">
-        <v>0.1100665823062016</v>
-      </c>
-      <c r="E46">
-        <v>0.22003709962520901</v>
-      </c>
-      <c r="F46">
-        <v>0.22984968959728599</v>
-      </c>
-      <c r="G46">
-        <v>0.26889289634430008</v>
-      </c>
-      <c r="H46">
-        <v>0.29444495538528298</v>
-      </c>
-      <c r="I46">
-        <v>0.32502751159068799</v>
-      </c>
-      <c r="J46">
-        <v>0.47268821803536409</v>
-      </c>
-      <c r="K46">
-        <v>0.57072979697429838</v>
-      </c>
-      <c r="L46">
-        <v>0.65055552939835171</v>
-      </c>
-      <c r="M46">
-        <v>0.68091040389652602</v>
-      </c>
-      <c r="N46">
-        <v>0.70431628000588575</v>
-      </c>
-      <c r="O46">
-        <v>0.70614468729651703</v>
-      </c>
-      <c r="P46">
-        <v>0.70682184904374123</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>3.1521518801736037E-2</v>
-      </c>
-      <c r="C47">
-        <v>0.10045720977442681</v>
-      </c>
-      <c r="D47">
-        <v>0.13591656618461981</v>
-      </c>
-      <c r="E47">
-        <v>0.20399045255907119</v>
-      </c>
-      <c r="F47">
-        <v>0.30873136132140733</v>
-      </c>
-      <c r="G47">
-        <v>0.35877347864965931</v>
-      </c>
-      <c r="H47">
-        <v>0.36325152090395307</v>
-      </c>
-      <c r="I47">
-        <v>0.37765260719774169</v>
-      </c>
-      <c r="J47">
-        <v>0.41402638469874781</v>
-      </c>
-      <c r="K47">
-        <v>0.50100278852752811</v>
-      </c>
-      <c r="L47">
-        <v>0.54989813128927967</v>
-      </c>
-      <c r="M47">
-        <v>0.5970612893696885</v>
-      </c>
-      <c r="N47">
-        <v>0.62001837265022985</v>
-      </c>
-      <c r="O47">
-        <v>0.64036110649946543</v>
-      </c>
-      <c r="P47">
-        <v>0.68149983101023914</v>
+        <v>0.66654070451182579</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P31 B33:P47 B32:J32 L32:P32">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="B2:P43">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0.2</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0.2</formula>
     </cfRule>
   </conditionalFormatting>
